--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104626_W19.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104626_W19.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. TOMIC</t>
+          <t>R. RUBIO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2209</v>
+        <v>5.2164</v>
       </c>
       <c r="E2" t="n">
-        <v>2.6648</v>
+        <v>2.4171</v>
       </c>
       <c r="F2" t="n">
-        <v>2.556</v>
+        <v>2.7993</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6575</v>
+        <v>5.0147</v>
       </c>
       <c r="H2" t="n">
-        <v>1.4472</v>
+        <v>5.3486</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2103</v>
+        <v>-0.3338</v>
       </c>
       <c r="J2" t="n">
-        <v>1.1319</v>
+        <v>4.61</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9453</v>
+        <v>5.1915</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1866</v>
+        <v>-0.5816</v>
       </c>
       <c r="M2" t="n">
-        <v>1.5256</v>
+        <v>0.4048</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5019</v>
+        <v>0.157</v>
       </c>
       <c r="O2" t="n">
-        <v>1.0237</v>
+        <v>0.2477</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4537</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4537</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4613</v>
+        <v>-0.0684</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9739</v>
+        <v>0.1321</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5125999999999999</v>
+        <v>-0.2005</v>
       </c>
       <c r="V2" t="n">
-        <v>2.571</v>
+        <v>1.8634</v>
       </c>
       <c r="W2" t="n">
-        <v>2.5068</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. RUZIC</t>
+          <t>A. TOMIC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6738</v>
+        <v>4.8696</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7685</v>
+        <v>3.0639</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.0947</v>
+        <v>1.8057</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.5429</v>
+        <v>2.6738</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4877</v>
+        <v>1.4502</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.0307</v>
+        <v>1.2236</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2162</v>
+        <v>1.1202</v>
       </c>
       <c r="K3" t="n">
-        <v>2.677</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.4608</v>
+        <v>0.1862</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.7592</v>
+        <v>1.5536</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.1893</v>
+        <v>0.5162</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.5699</v>
+        <v>1.0374</v>
       </c>
       <c r="P3" t="n">
-        <v>2.2683</v>
+        <v>0.4553</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2683</v>
+        <v>0.4553</v>
       </c>
       <c r="S3" t="n">
-        <v>4.7877</v>
+        <v>-0.8253</v>
       </c>
       <c r="T3" t="n">
-        <v>4.3915</v>
+        <v>-0.5508</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3962</v>
+        <v>-0.2745</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1607</v>
+        <v>2.5659</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1607</v>
+        <v>2.4945</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.07140000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. RUBIO</t>
+          <t>H. DRELL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.0009</v>
+        <v>2.6748</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5797</v>
+        <v>0.4688</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4212</v>
+        <v>2.206</v>
       </c>
       <c r="G4" t="n">
-        <v>5.0317</v>
+        <v>1.2967</v>
       </c>
       <c r="H4" t="n">
-        <v>5.3622</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3306</v>
+        <v>0.6138</v>
       </c>
       <c r="J4" t="n">
-        <v>4.6547</v>
+        <v>0.346</v>
       </c>
       <c r="K4" t="n">
-        <v>5.2225</v>
+        <v>0.1379</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5679</v>
+        <v>0.2081</v>
       </c>
       <c r="M4" t="n">
-        <v>0.377</v>
+        <v>0.9507</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1397</v>
+        <v>0.5451</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2373</v>
+        <v>0.4057</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.5878</v>
+        <v>0.6829</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.4025</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8147</v>
+        <v>0.6829</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.3069</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7652</v>
+        <v>0.1228</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5417</v>
+        <v>-0.2016</v>
       </c>
       <c r="V4" t="n">
-        <v>1.8639</v>
+        <v>0.7739</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H. DRELL</t>
+          <t>S. BIRGANDER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.6734</v>
+        <v>1.9202</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3037</v>
+        <v>3.195</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3697</v>
+        <v>-1.2748</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2853</v>
+        <v>-0.8974</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6722</v>
+        <v>0.8823</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6131</v>
+        <v>-1.7797</v>
       </c>
       <c r="J5" t="n">
-        <v>0.357</v>
+        <v>2.3707</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1385</v>
+        <v>2.3335</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2185</v>
+        <v>0.0372</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9283</v>
+        <v>-3.2681</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5337</v>
+        <v>-1.4511</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3946</v>
+        <v>-1.8169</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6805</v>
+        <v>2.0487</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6805</v>
+        <v>2.0487</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9364</v>
+        <v>0.9266</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9467</v>
+        <v>0.8242</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0103</v>
+        <v>0.1024</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7712</v>
+        <v>-0.1578</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.7712</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. BIRGANDER</t>
+          <t>M. RUZIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9984</v>
+        <v>1.5693</v>
       </c>
       <c r="E6" t="n">
-        <v>2.5558</v>
+        <v>2.9384</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.5575</v>
+        <v>-1.3691</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8951</v>
+        <v>-2.5369</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8934</v>
+        <v>0.4882</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.7885</v>
+        <v>-3.0252</v>
       </c>
       <c r="J6" t="n">
-        <v>2.3955</v>
+        <v>1.1902</v>
       </c>
       <c r="K6" t="n">
-        <v>2.3582</v>
+        <v>2.6577</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0373</v>
+        <v>-1.4676</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.2906</v>
+        <v>-3.7271</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.4648</v>
+        <v>-2.1695</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.8258</v>
+        <v>-1.5576</v>
       </c>
       <c r="P6" t="n">
-        <v>2.0415</v>
+        <v>2.2763</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0415</v>
+        <v>2.2763</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0127</v>
+        <v>1.6721</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1603</v>
+        <v>1.5905</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1476</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1571</v>
+        <v>0.4327</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3402</v>
+        <v>0.5652</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4973</v>
+        <v>-0.1324</v>
       </c>
       <c r="G7" t="n">
-        <v>1.3301</v>
+        <v>1.3407</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3304</v>
+        <v>0.3303</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9997</v>
+        <v>1.0104</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0191</v>
+        <v>-0.0257</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.09370000000000001</v>
+        <v>-0.1002</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M7" t="n">
-        <v>1.3492</v>
+        <v>1.3664</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4241</v>
+        <v>0.4305</v>
       </c>
       <c r="O7" t="n">
-        <v>0.925</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3946</v>
+        <v>-0.8185</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3478</v>
+        <v>-0.1116</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.0468</v>
+        <v>-0.7069</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W7" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="8">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1141</v>
+        <v>-1.0419</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1996</v>
+        <v>-0.1537</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9145</v>
+        <v>-0.8882</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.9005</v>
+        <v>-1.9012</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.642</v>
+        <v>-1.6482</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2585</v>
+        <v>-0.253</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0574</v>
+        <v>0.0325</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3503</v>
+        <v>-0.3695</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4078</v>
+        <v>0.4019</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.9579</v>
+        <v>-1.9337</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2917</v>
+        <v>-1.2788</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6663</v>
+        <v>-0.6549</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.121</v>
+        <v>-0.0512</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2571</v>
+        <v>-0.1862</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1361</v>
+        <v>0.135</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4449</v>
+        <v>-1.6906</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8743</v>
+        <v>-2.0004</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4294</v>
+        <v>0.3098</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4695</v>
+        <v>-1.4582</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0968</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.3727</v>
+        <v>-1.3688</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6775</v>
+        <v>0.6623</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7548</v>
+        <v>0.7444</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.07729999999999999</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.147</v>
+        <v>-2.1205</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8516</v>
+        <v>-0.8339</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.2954</v>
+        <v>-1.2866</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8393</v>
+        <v>0.5887</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5293</v>
+        <v>0.4363</v>
       </c>
       <c r="U9" t="n">
-        <v>0.31</v>
+        <v>0.1524</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X9" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="10">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.0247</v>
+        <v>-2.2363</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7987</v>
+        <v>-1.3049</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.226</v>
+        <v>-0.9315</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.6036</v>
+        <v>-3.6115</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.3059</v>
+        <v>-1.3067</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.2977</v>
+        <v>-2.3047</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.399</v>
+        <v>-0.4452</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5848</v>
+        <v>0.5613</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.9838</v>
+        <v>-1.0065</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.2046</v>
+        <v>-3.1663</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.8906</v>
+        <v>-1.8681</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.314</v>
+        <v>-1.2982</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R10" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.926</v>
+        <v>-0.1209</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1825</v>
+        <v>0.3758</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7433999999999999</v>
+        <v>-0.4967</v>
       </c>
       <c r="V10" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W10" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1007</v>
+        <v>-3.2723</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6103</v>
+        <v>-2.0527</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4904</v>
+        <v>-1.2196</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2542</v>
+        <v>-0.2551</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4602</v>
+        <v>0.4677</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7144</v>
+        <v>-0.7228</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1233</v>
+        <v>0.1009</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9177999999999999</v>
+        <v>0.9136</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7945</v>
+        <v>-0.8126</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3776</v>
+        <v>-0.356</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4576</v>
+        <v>-0.4458</v>
       </c>
       <c r="O11" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.805</v>
+        <v>-0.9685</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6261</v>
+        <v>-0.0351</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.1789</v>
+        <v>-0.9334</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.725899999999999</v>
+        <v>8.441900000000002</v>
       </c>
       <c r="E12" t="n">
-        <v>6.729799999999999</v>
+        <v>7.136699999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9959</v>
+        <v>1.305200000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3611999999999997</v>
+        <v>-0.3344000000000004</v>
       </c>
       <c r="H12" t="n">
-        <v>6.6086</v>
+        <v>6.606</v>
       </c>
       <c r="I12" t="n">
-        <v>-6.97</v>
+        <v>-6.9402</v>
       </c>
       <c r="J12" t="n">
-        <v>10.1954</v>
+        <v>9.961899999999998</v>
       </c>
       <c r="K12" t="n">
-        <v>13.1549</v>
+        <v>13.0042</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.9595</v>
+        <v>-3.0425</v>
       </c>
       <c r="M12" t="n">
-        <v>-10.5568</v>
+        <v>-10.2962</v>
       </c>
       <c r="N12" t="n">
-        <v>-6.546200000000001</v>
+        <v>-6.398400000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-4.0108</v>
+        <v>-3.8976</v>
       </c>
       <c r="P12" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q12" t="n">
-        <v>-12.4758</v>
+        <v>-12.5198</v>
       </c>
       <c r="R12" t="n">
-        <v>13.61</v>
+        <v>13.658</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4386999999999994</v>
+        <v>0.2558999999999997</v>
       </c>
       <c r="T12" t="n">
-        <v>1.8752</v>
+        <v>2.598</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.3138</v>
+        <v>-2.3422</v>
       </c>
       <c r="V12" t="n">
-        <v>7.391399999999999</v>
+        <v>7.382099999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>7.1347</v>
+        <v>7.096500000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>0.2567</v>
+        <v>0.2856000000000002</v>
       </c>
     </row>
     <row r="13">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.8116</v>
+        <v>3.186</v>
       </c>
       <c r="E13" t="n">
-        <v>3.0414</v>
+        <v>1.2351</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7702</v>
+        <v>1.9509</v>
       </c>
       <c r="G13" t="n">
-        <v>1.9425</v>
+        <v>1.9284</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3912</v>
+        <v>0.3825</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5513</v>
+        <v>1.546</v>
       </c>
       <c r="J13" t="n">
-        <v>1.6164</v>
+        <v>1.5818</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9902</v>
+        <v>0.9718</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6263</v>
+        <v>0.61</v>
       </c>
       <c r="M13" t="n">
-        <v>0.326</v>
+        <v>0.3467</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.599</v>
+        <v>-0.5893</v>
       </c>
       <c r="O13" t="n">
-        <v>0.925</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R13" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S13" t="n">
-        <v>3.6157</v>
+        <v>2.0103</v>
       </c>
       <c r="T13" t="n">
-        <v>3.5326</v>
+        <v>1.7718</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0832</v>
+        <v>0.2385</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3172</v>
+        <v>1.4892</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2453</v>
+        <v>0.195</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0718</v>
+        <v>1.2941</v>
       </c>
       <c r="G14" t="n">
-        <v>1.7338</v>
+        <v>1.7144</v>
       </c>
       <c r="H14" t="n">
-        <v>2.0723</v>
+        <v>2.0572</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3386</v>
+        <v>-0.3428</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9613</v>
+        <v>2.9178</v>
       </c>
       <c r="K14" t="n">
-        <v>3.3799</v>
+        <v>3.3505</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.4186</v>
+        <v>-0.4326</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.2275</v>
+        <v>-1.2034</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.3075</v>
+        <v>-1.2932</v>
       </c>
       <c r="O14" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R14" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1051</v>
+        <v>1.2983</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6866</v>
+        <v>0.6917</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4186</v>
+        <v>0.6066</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0289</v>
+        <v>1.0428</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.4233</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4522</v>
+        <v>1.5986</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.273</v>
+        <v>-0.2744</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2308</v>
+        <v>0.2353</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5038</v>
+        <v>-0.5097</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.375</v>
+        <v>-0.3906</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6407</v>
+        <v>0.6378</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.0157</v>
+        <v>-1.0284</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1019</v>
+        <v>0.1162</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4099</v>
+        <v>-0.4025</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5118</v>
+        <v>0.5187</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5553</v>
+        <v>0.5644</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0484</v>
+        <v>-0.1652</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6037</v>
+        <v>0.7297</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3251</v>
+        <v>0.72</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2791</v>
+        <v>2.8228</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6042</v>
+        <v>-2.1028</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3428</v>
+        <v>4.2612</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.9176</v>
+        <v>-0.3536</v>
       </c>
       <c r="I16" t="n">
-        <v>2.2604</v>
+        <v>4.6147</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6021</v>
+        <v>5.2369</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.2637</v>
+        <v>1.1409</v>
       </c>
       <c r="L16" t="n">
-        <v>1.8658</v>
+        <v>4.0961</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2593</v>
+        <v>-0.9758</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.6539</v>
+        <v>-1.4945</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3946</v>
+        <v>0.5187</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.6805</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5878</v>
+        <v>0.2276</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8235</v>
+        <v>-1.5411</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3871</v>
+        <v>-0.5021</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4364</v>
+        <v>-1.0391</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1607</v>
+        <v>-1.0895</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>-0.7739</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1607</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. NOGUES</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2441</v>
+        <v>0.2781</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0173</v>
+        <v>0.0475</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2268</v>
+        <v>0.2305</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0173</v>
+        <v>0.3463</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0173</v>
+        <v>-1.9212</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>2.2675</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0173</v>
+        <v>1.5786</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0173</v>
+        <v>-0.2833</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.8618</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>-1.2323</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-1.638</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>0.4057</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2268</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2268</v>
+        <v>1.5934</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>0.7725</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>0.7453</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.0272</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>I. NOGUES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0319</v>
+        <v>0.2449</v>
       </c>
       <c r="E18" t="n">
-        <v>2.3787</v>
+        <v>0.0172</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.4106</v>
+        <v>0.2276</v>
       </c>
       <c r="G18" t="n">
-        <v>4.2573</v>
+        <v>0.0172</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3594</v>
+        <v>0.0172</v>
       </c>
       <c r="I18" t="n">
-        <v>4.6167</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>5.258</v>
+        <v>0.0172</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1531</v>
+        <v>0.0172</v>
       </c>
       <c r="L18" t="n">
-        <v>4.1048</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0007</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.5125</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5118</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.2892</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9739</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.3153</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.7712</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. KEY</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2248</v>
+        <v>-0.3065</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6544</v>
+        <v>-1.0185</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8793</v>
+        <v>0.712</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0648</v>
+        <v>0.2621</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1297</v>
+        <v>-0.0717</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1946</v>
+        <v>0.3338</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4941</v>
+        <v>0.75</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5715</v>
+        <v>0.6755</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.07729999999999999</v>
+        <v>0.0745</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-0.4879</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4417</v>
+        <v>-0.7472</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1172</v>
+        <v>0.2593</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2268</v>
+        <v>1.5934</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3868</v>
+        <v>0.6818</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1603</v>
+        <v>-0.0141</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5471</v>
+        <v>0.6959</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.7057</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.6162</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>B. KEY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2496</v>
+        <v>-0.6047</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4714</v>
+        <v>0.2937</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2218</v>
+        <v>-0.8984</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2599</v>
+        <v>-0.0577</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0707</v>
+        <v>0.1374</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3306</v>
+        <v>-0.1952</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7602</v>
+        <v>0.4867</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6856</v>
+        <v>0.5688</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0746</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5003</v>
+        <v>-0.5444</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7563</v>
+        <v>-0.4314</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2559</v>
+        <v>-0.113</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5878</v>
+        <v>0.2276</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7401</v>
+        <v>-0.7747000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4869</v>
+        <v>-0.193</v>
       </c>
       <c r="U20" t="n">
-        <v>1.227</v>
+        <v>-0.5816</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.7032</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.6105</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8784</v>
+        <v>-0.7654</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2372</v>
+        <v>0.3057</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1155</v>
+        <v>-1.0712</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5168</v>
+        <v>0.5101</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.163</v>
+        <v>-0.1691</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6797</v>
+        <v>0.6792</v>
       </c>
       <c r="J21" t="n">
-        <v>1.5569</v>
+        <v>1.5132</v>
       </c>
       <c r="K21" t="n">
-        <v>1.9008</v>
+        <v>1.8713</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.344</v>
+        <v>-0.3581</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0401</v>
+        <v>-1.0031</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.0638</v>
+        <v>-2.0405</v>
       </c>
       <c r="O21" t="n">
-        <v>1.0237</v>
+        <v>1.0374</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6654</v>
+        <v>-0.5503</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0393</v>
+        <v>0.1599</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7047</v>
+        <v>-0.7102000000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.8639</v>
+        <v>-1.8634</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.2249</v>
+        <v>-0.2292</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="22">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2354</v>
+        <v>-3.0969</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7782</v>
+        <v>-2.5597</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4571</v>
+        <v>-0.5372</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.8215</v>
+        <v>-4.8286</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.1053</v>
+        <v>-2.1052</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.7162</v>
+        <v>-2.7233</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.8225</v>
+        <v>-3.8393</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.5381</v>
+        <v>-1.5448</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.2844</v>
+        <v>-2.2945</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.999</v>
+        <v>-0.9893</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5672</v>
+        <v>-0.5604</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4318</v>
+        <v>-0.4289</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4274</v>
+        <v>0.5724</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0484</v>
+        <v>0.1901</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4757</v>
+        <v>0.3823</v>
       </c>
       <c r="V22" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. THOMPSON</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.1292</v>
+        <v>-4.5821</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8895</v>
+        <v>0.1737</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.2397</v>
+        <v>-4.7558</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.8135</v>
+        <v>-0.7405</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.0001</v>
+        <v>-1.8243</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1866</v>
+        <v>1.0838</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6374</v>
+        <v>1.0959</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.1571</v>
+        <v>0.1584</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.9375</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.1761</v>
+        <v>-1.8364</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.8429</v>
+        <v>-1.9827</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3331</v>
+        <v>0.1463</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2231</v>
+        <v>-1.136</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1179</v>
+        <v>0.1297</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.1051</v>
+        <v>-1.2656</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0927</v>
+        <v>-2.2504</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.0863</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0927</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>D. THOMPSON</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.7033</v>
+        <v>-5.3501</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.7287</v>
+        <v>-2.2619</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.9746</v>
+        <v>-3.0882</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.7361</v>
+        <v>-2.8042</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.8342</v>
+        <v>-2.9904</v>
       </c>
       <c r="I24" t="n">
-        <v>1.0981</v>
+        <v>0.1862</v>
       </c>
       <c r="J24" t="n">
-        <v>1.1255</v>
+        <v>-0.652</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1661</v>
+        <v>-1.1656</v>
       </c>
       <c r="L24" t="n">
-        <v>0.9594</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.8615</v>
+        <v>-2.1522</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.0002</v>
+        <v>-1.8248</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1387</v>
+        <v>-0.3275</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.4537</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.2641</v>
+        <v>-1.4565</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8166</v>
+        <v>-0.4718</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.4475</v>
+        <v>-0.9846</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.2495</v>
+        <v>-1.0895</v>
       </c>
       <c r="W24" t="n">
-        <v>0.0965</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.3461</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.7257</v>
+        <v>-7.7447</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.9959000000000008</v>
+        <v>-1.3053</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.729799999999999</v>
+        <v>-6.4399</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3614999999999995</v>
+        <v>0.3342999999999998</v>
       </c>
       <c r="H25" t="n">
-        <v>-6.609000000000001</v>
+        <v>-6.6059</v>
       </c>
       <c r="I25" t="n">
-        <v>6.9702</v>
+        <v>6.9402</v>
       </c>
       <c r="J25" t="n">
-        <v>10.5569</v>
+        <v>10.2962</v>
       </c>
       <c r="K25" t="n">
-        <v>6.5463</v>
+        <v>6.398500000000002</v>
       </c>
       <c r="L25" t="n">
-        <v>4.0106</v>
+        <v>3.897799999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>-10.1956</v>
+        <v>-9.9619</v>
       </c>
       <c r="N25" t="n">
-        <v>-13.1549</v>
+        <v>-13.0045</v>
       </c>
       <c r="O25" t="n">
-        <v>2.9594</v>
+        <v>3.0425</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q25" t="n">
-        <v>-13.6101</v>
+        <v>-13.6581</v>
       </c>
       <c r="R25" t="n">
-        <v>12.4756</v>
+        <v>12.5196</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4384999999999994</v>
+        <v>0.4411</v>
       </c>
       <c r="T25" t="n">
-        <v>2.3138</v>
+        <v>2.3423</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.8751</v>
+        <v>-1.9009</v>
       </c>
       <c r="V25" t="n">
-        <v>-7.391399999999999</v>
+        <v>-7.3824</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.2566999999999999</v>
+        <v>-0.2857000000000001</v>
       </c>
       <c r="X25" t="n">
-        <v>-7.1347</v>
+        <v>-7.0966</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104626_W19.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104626_W19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104626_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0.07140000000000001</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104626_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104626_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104626_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104626_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104626_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104626_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104626_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104626_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104626_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>0.2856000000000002</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104626_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104626_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104626_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104626_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104626_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104626_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104626_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104626_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104626_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104626_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104626_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104626_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-7.0966</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
